--- a/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
+++ b/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:41:47+00:00</t>
+    <t>2026-07-26T06:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
+++ b/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:50:53+00:00</t>
+    <t>2026-07-26T06:54:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
+++ b/branches/chore/org-kebab/StructureDefinition-example-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:54:38+00:00</t>
+    <t>2026-07-26T06:58:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
